--- a/Repository/Settings/Translations.xlsx
+++ b/Repository/Settings/Translations.xlsx
@@ -929,7 +929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D496"/>
+  <dimension ref="A1:D498"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -9379,6 +9379,40 @@
         </is>
       </c>
     </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>Report</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>{0} point(s) displayed</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>{0} point(s) affiché(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>Report</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>{0} row(s) without coordinates</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>{0} ligne(s) sans coordonnées</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D503"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Repository/Settings/Translations.xlsx
+++ b/Repository/Settings/Translations.xlsx
@@ -929,7 +929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D498"/>
+  <dimension ref="A1:D499"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -9413,6 +9413,23 @@
         </is>
       </c>
     </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>Report</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>Reset restrictions</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>Réinitialiser les restrictions</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D503"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Repository/Settings/Translations.xlsx
+++ b/Repository/Settings/Translations.xlsx
@@ -929,7 +929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D499"/>
+  <dimension ref="A1:D500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -9430,6 +9430,23 @@
         </is>
       </c>
     </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>The report '{0}' was not found: it has not been created or it was moved.</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>Le rapport '{0}' est introuvable : il n'a pas été créé ou il a été déplacé.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D503"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Repository/Settings/Translations.xlsx
+++ b/Repository/Settings/Translations.xlsx
@@ -929,7 +929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D500"/>
+  <dimension ref="A1:D520"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -9447,6 +9447,346 @@
         </is>
       </c>
     </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>Report</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>This key already exists</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>Cette clé existe déjà</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>Report</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>A record with the same key or unique value already exists</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>Un enregistrement avec la même clé ou valeur unique existe déjà</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>Report</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>Record not found</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>Enregistrement introuvable</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>Report</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>This operation is not allowed</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>Cette opération n'est pas autorisée</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>Report</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>No record has been modified</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>Aucun enregistrement n'a été modifié</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>Report</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>Invalid value</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>Valeur invalide</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>Report</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>An error occurred</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>Une erreur s'est produite</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>Report</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>Unable to reach the server</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>Impossible de joindre le serveur</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>Report</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>Your session has expired, please reload the page</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>Votre session a expiré, veuillez recharger la page</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>Report</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>Are you sure you want to delete this record?</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>Voulez-vous vraiment supprimer cet enregistrement ?</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>Report</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>Edit record</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>Modifier l'enregistrement</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>Report</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>New record</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>Nouvel enregistrement</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>Report</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>The record has been created</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>L'enregistrement a été créé</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>Report</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>The record has been deleted</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>L'enregistrement a été supprimé</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>Report</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>The record has been saved</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>L'enregistrement a été enregistré</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>Report</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>The table cannot be edited here</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>La table ne peut pas être modifiée ici</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>Report</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>Delete</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>Supprimer</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>Report</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>Modifier</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>Report</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>Nouveau</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>Report</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>Save</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>Enregistrer</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D503"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Repository/Settings/Translations.xlsx
+++ b/Repository/Settings/Translations.xlsx
@@ -929,7 +929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D520"/>
+  <dimension ref="A1:D523"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -9787,6 +9787,57 @@
         </is>
       </c>
     </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>You have been signed out.</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>Vous avez été déconnecté.</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>Show password</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>Afficher le mot de passe</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>or</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>ou</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D503"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Repository/Settings/Translations.xlsx
+++ b/Repository/Settings/Translations.xlsx
@@ -929,7 +929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D523"/>
+  <dimension ref="A1:D525"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -9838,6 +9838,40 @@
         </is>
       </c>
     </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>Error: the report cannot be uploaded, it contains content above your authorization level ({0}): {1}</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>Erreur : le rapport ne peut pas être chargé, il contient du contenu au-delà de votre niveau d'autorisation ({0}) : {1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>Error: the file cannot be renamed as a report, it contains content above your authorization level ({0}): {1}</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>Erreur : le fichier ne peut pas être renommé en rapport, il contient du contenu au-delà de votre niveau d'autorisation ({0}) : {1}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D503"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Repository/Settings/Translations.xlsx
+++ b/Repository/Settings/Translations.xlsx
@@ -929,7 +929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D525"/>
+  <dimension ref="A1:D543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -9872,6 +9872,312 @@
         </is>
       </c>
     </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>MCP access tokens</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>Jetons d'accès MCP</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>A personal access token connects an AI client (Claude, Copilot, Cursor...) to the AI agents with your rights: set it in the header 'Authorization: Bearer &lt;token&gt;' of the MCP server URL.</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>Un jeton d'accès personnel connecte un client IA (Claude, Copilot, Cursor...) aux agents IA avec vos droits : indiquez-le dans l'en-tête 'Authorization: Bearer &lt;jeton&gt;' de l'URL du serveur MCP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>Created</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>Créé le</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>Expires</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>Expire le</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>Last use</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>Dernière utilisation</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>Token name (e.g. Claude Code)</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>Nom du jeton (ex. Claude Code)</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>Créer</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>Copy this token now: it will not be shown again.</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>Copiez ce jeton maintenant : il ne sera plus affiché.</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>MCP server URLs of your agents:</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>URL du serveur MCP de vos agents :</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>Never</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>Jamais</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>The MCP server is not available for your user.</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>Le serveur MCP n'est pas disponible pour votre utilisateur.</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>The MCP access tokens are not available for your authentication.</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>Les jetons d'accès MCP ne sont pas disponibles pour votre authentification.</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>The validity of the token must be between 1 and {0} days.</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>La validité du jeton doit être comprise entre 1 et {0} jours.</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>The access token has not been found.</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>Le jeton d'accès n'a pas été trouvé.</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>WebJS</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>Revoke</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>Révoquer</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>WebJS</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>Revoke this access token? The AI clients using it will no longer be connected.</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>Révoquer ce jeton d'accès ? Les clients IA qui l'utilisent ne seront plus connectés.</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>WebJS</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>days</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>jours</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>WebJS</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>No expiration</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>Sans expiration</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D503"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Repository/Settings/Translations.xlsx
+++ b/Repository/Settings/Translations.xlsx
@@ -929,7 +929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D543"/>
+  <dimension ref="A1:D544"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -10178,6 +10178,23 @@
         </is>
       </c>
     </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>MCP access</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>Accès MCP</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D503"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Repository/Settings/Translations.xlsx
+++ b/Repository/Settings/Translations.xlsx
@@ -929,7 +929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D544"/>
+  <dimension ref="A1:D571"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -10195,6 +10195,465 @@
         </is>
       </c>
     </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>Authorize an AI client</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>Autoriser un client IA</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>requests access to the AI agent</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>demande l'accès à l'agent IA</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>with your rights.</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>avec vos droits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>After your authorization, you will be redirected to:</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>Après votre autorisation, vous serez redirigé vers :</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>This client is an application of your computer (local address). Authorize it only if you have just started the connection from an AI client you trust, e.g. Claude Code.</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>Ce client est une application de votre ordinateur (adresse locale). Ne l'autorisez que si vous venez de lancer la connexion depuis un client IA de confiance, par exemple Claude Code.</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>Log in to authorize the client</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>Connectez-vous pour autoriser le client</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>Log in</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>Se connecter</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>Log in with single sign-on</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>Se connecter avec l'authentification unique (SSO)</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>Logged in as</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>Connecté en tant que</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>The authorization of an AI client requires a login with the Two-Factor Authentication or with the single sign-on.</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>L'autorisation d'un client IA nécessite une connexion avec l'authentification à deux facteurs ou avec l'authentification unique (SSO).</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>The client will be able to use these tools:</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>Le client pourra utiliser ces outils :</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>Read only</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>Lecture seule</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>Write</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>Écriture</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>Modify or delete</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>Modification ou suppression</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>The data returned by the tools are sent to the AI model of the client. You can revoke this authorization at any time in your profile ('MCP access').</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>Les données retournées par les outils sont envoyées au modèle IA du client. Vous pouvez révoquer cette autorisation à tout moment dans votre profil (« Accès MCP »).</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>Deny</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>Refuser</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>Authorize</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>Autoriser</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>The agent '{0}' is not available on the MCP server for your user.</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>L'agent '{0}' n'est pas disponible sur le serveur MCP pour votre utilisateur.</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>This authorization request has expired. Please connect again from your AI client.</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>Cette demande d'autorisation a expiré. Veuillez vous reconnecter depuis votre client IA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>The authorization has not been found.</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>L'autorisation est introuvable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>Authorized applications</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>Applications autorisées</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>AI clients connected with OAuth: add the MCP server URL of an agent as a connector in your AI client (e.g. claude.ai or Claude Desktop) and log in to authorize it.</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>Clients IA connectés avec OAuth : ajoutez l'URL du serveur MCP d'un agent comme connecteur dans votre client IA (par exemple claude.ai ou Claude Desktop) et connectez-vous pour l'autoriser.</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>Application</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>Application</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>Authorized</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>Autorisé le</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>No application authorized.</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>Aucune application autorisée.</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>WebJS</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>Revoke this authorization? The AI client will no longer be connected.</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>Révoquer cette autorisation ? Le client IA ne sera plus connecté.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D503"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Repository/Settings/Translations.xlsx
+++ b/Repository/Settings/Translations.xlsx
@@ -929,7 +929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D571"/>
+  <dimension ref="A1:D652"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -10654,6 +10654,1383 @@
         </is>
       </c>
     </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>My schedules</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>Mes planifications</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>To schedule a report, open the list of its views and outputs and choose 'Schedule...'.</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>Pour planifier un rapport, ouvrez la liste de ses vues et sorties et choisissez 'Planifier...'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>Destination</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>Destination</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>Recurrence</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>Récurrence</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>Next execution</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>Prochaine exécution</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>Last execution</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>Dernière exécution</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>You have no schedule.</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>Vous n'avez aucune planification.</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>Activée</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>Résultat</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>Format</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>Format</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>To</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>À</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>Email addresses separated by semi-column</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>Adresses email séparées par un point-virgule</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>BCC</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>CCI</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>Subject</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>Objet</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>Report name if empty</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>Nom du rapport si vide</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>Body</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>Corps</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>Default text if empty</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>Texte par défaut si vide</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>Copy the HTML result in the email body</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>Copier le résultat HTML dans le corps de l'email</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>Folder</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>Dossier</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>File name</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>Nom du fichier</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>Compress the result (zip)</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>Compresser le résultat (zip)</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>Zip password</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>Mot de passe du zip</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>Remove the password</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>Supprimer le mot de passe</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>Cancel the generation if there is no record</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>Annuler la génération s'il n'y a aucun enregistrement</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>One time</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>Une fois</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>Quotidien</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>Hebdomadaire</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>Mensuel</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>Start</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>Début</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>End (optional)</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>Fin (optionnelle)</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>Days of the week</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>Jours de la semaine</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>Months</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>Mois</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>Days of the month</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>Jours du mois</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>Advanced</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>Avancé</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>Repeat every</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>Répéter toutes les</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>For a duration of</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>Pendant une durée de</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>The schedule has been deleted</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>La planification a été supprimée</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>You are not allowed to schedule reports</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>Vous n'êtes pas autorisé à planifier des rapports</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>The schedule has not been found</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>La planification est introuvable</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>The report does not exist</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>Le rapport n'existe pas</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>Unknown device</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>Périphérique inconnu</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>You have no right to write in this folder</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>Vous n'avez pas le droit d'écrire dans ce dossier</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>Every {0} days</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>Tous les {0} jours</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>Every {0} weeks</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>Toutes les {0} semaines</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>Last</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>Dernier</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>repeated every {0} minutes</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>répété toutes les {0} minutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>Please select an output device</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>Veuillez choisir une destination</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>The format is not allowed</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>Ce format n'est pas autorisé</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>Please define the email destination</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>Veuillez définir le destinataire de l'email</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>Please define the file name</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>Veuillez définir le nom du fichier</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>The file name is invalid</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>Le nom du fichier est invalide</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>Please select a folder</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>Veuillez choisir un dossier</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>Please select a directory</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>Veuillez choisir un répertoire</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>The start date is invalid</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>La date de début est invalide</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>The end date is invalid</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>La date de fin est invalide</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>The end date is before the start date</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>La date de fin est antérieure à la date de début</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>The recurrence is invalid</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>La récurrence est invalide</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>The interval must be greater than 0</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>L'intervalle doit être supérieur à 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>Please select at least one day of the week</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>Veuillez choisir au moins un jour de la semaine</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>Please select at least one month and one day</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>Veuillez choisir au moins un mois et un jour</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>Inconsistent duration or interval for the repetition</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>Durée ou intervalle de répétition incohérent</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>WebJS</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>jour</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>WebJS</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>hour</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>heure</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>WebJS</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>hours</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>heures</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>WebJS</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>minutes</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>minutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>WebJS</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>Indefinitely</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>Indéfiniment</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>WebJS</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>Recur every (weeks)</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>Répéter toutes les (semaines)</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>WebJS</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>Recur every (days)</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>Répéter tous les (jours)</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>WebJS</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>New schedule</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>Nouvelle planification</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>WebJS</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>Password unchanged</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>Mot de passe inchangé</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>WebJS</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>Zip password</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>Mot de passe du zip</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>WebJS</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>Last</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>Dernier</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>WebJS</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>The schedule has been saved</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>La planification a été enregistrée</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>WebJS</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>Next execution</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>Prochaine exécution</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>WebJS</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>Do you really want to delete the schedule</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>Voulez-vous vraiment supprimer la planification</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>WebJS</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>Disabled</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>Désactivée</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>WebJS</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>Modifier</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>WebJS</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>Execute now</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>Exécuter maintenant</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>WebJS</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>Schedule...</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>Planifier...</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>You have no right to schedule this report</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>Vous n'avez pas le droit de planifier ce rapport</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D503"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Repository/Settings/Translations.xlsx
+++ b/Repository/Settings/Translations.xlsx
@@ -929,7 +929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D652"/>
+  <dimension ref="A1:D654"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -12031,6 +12031,40 @@
         </is>
       </c>
     </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>File names with the execution date time</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>Noms de fichier avec la date et l'heure d'exécution</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>The format of the execution date in the file name is invalid</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>Le format de la date d'exécution dans le nom du fichier est invalide</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D503"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Repository/Settings/Translations.xlsx
+++ b/Repository/Settings/Translations.xlsx
@@ -929,7 +929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D654"/>
+  <dimension ref="A1:D666"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -12065,6 +12065,210 @@
         </is>
       </c>
     </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>Restrictions</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>Restrictions</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>Edit restrictions</t>
+        </is>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>Modifier les restrictions</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>Default values</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>Valeurs par défaut</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>Save the schedule and open the report to edit the values of its restrictions</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>Enregistrer la planification et ouvrir le rapport pour modifier les valeurs de ses restrictions</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>The restriction values have been saved for the schedule</t>
+        </is>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>Les valeurs des restrictions ont été enregistrées pour la planification</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>Please check the restriction values</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>Veuillez vérifier les valeurs des restrictions</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>The default values of the report are used</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>Les valeurs par défaut du rapport sont utilisées</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>The report is being executed</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>Le rapport est en cours d'exécution</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>WebJS</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>Default values of the report</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>Valeurs par défaut du rapport</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>WebJS</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>Edit the restrictions in the report window, then click on 'Save for the schedule'</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>Modifiez les restrictions dans la fenêtre du rapport, puis cliquez sur 'Enregistrer pour la planification'</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>Report</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>Save for the schedule</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>Enregistrer pour la planification</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>Report</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>Save the restriction values for the schedule</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>Enregistrer les valeurs des restrictions pour la planification</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D503"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Repository/Settings/Translations.xlsx
+++ b/Repository/Settings/Translations.xlsx
@@ -929,7 +929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D666"/>
+  <dimension ref="A1:D678"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -12269,6 +12269,210 @@
         </is>
       </c>
     </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>The AI budget is reached: the answer was interrupted.</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>Le budget IA est atteint : la réponse a été interrompue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>The costs of the AI provider are not configured: the AI budget of the user cannot be checked.</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>Les coûts du fournisseur IA ne sont pas configurés : le budget IA de l'utilisateur ne peut pas être vérifié.</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>The limits of the user cannot be checked, the message was not sent.</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>Les limites de l'utilisateur ne peuvent pas être vérifiées, le message n'a pas été envoyé.</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>WebJS</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>Never executed</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>Jamais exécutée</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>WebJS</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>Succès</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>WebJS</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>Executions of the report</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>Exécutions du rapport</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>WebJS</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>Invalid value for the repetition</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>Valeur invalide pour la répétition</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>WebJS</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>minute</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>minute</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>Duration</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>Durée</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>Statut</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>Executions</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>Exécutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>The audit is not enabled</t>
+        </is>
+      </c>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>L'audit n'est pas activé</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D503"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
